--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>_reportFile</t>
   </si>
@@ -59,6 +59,21 @@
   </si>
   <si>
     <t>https://www.ubs.com/in/en.html</t>
+  </si>
+  <si>
+    <t>uk/en.report.json</t>
+  </si>
+  <si>
+    <t>uk/en</t>
+  </si>
+  <si>
+    <t>2026-06-09T05:26:17.446Z</t>
+  </si>
+  <si>
+    <t>Our financial services in the United Kingdom | UBS United Kingdom</t>
+  </si>
+  <si>
+    <t>https://www.ubs.com/uk/en.html</t>
   </si>
 </sst>
 </file>
@@ -447,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -511,6 +526,32 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,19 +37,34 @@
     <t>url</t>
   </si>
   <si>
+    <t>global/en.report.json</t>
+  </si>
+  <si>
+    <t>["hero-homepage","cards-overview","cards-overview"]</t>
+  </si>
+  <si>
+    <t>global/en</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>homepage</t>
+  </si>
+  <si>
+    <t>2026-06-09T11:32:09.209Z</t>
+  </si>
+  <si>
+    <t>UBS financial services around the globe | UBS Global</t>
+  </si>
+  <si>
+    <t>https://www.ubs.com/global/en.html</t>
+  </si>
+  <si>
     <t>in/en.report.json</t>
   </si>
   <si>
-    <t>["hero-homepage","cards-overview","cards-overview"]</t>
-  </si>
-  <si>
     <t>in/en</t>
-  </si>
-  <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>homepage</t>
   </si>
   <si>
     <t>2026-06-08T12:26:47.933Z</t>
@@ -462,16 +477,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="8" max="8" width="36" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -550,6 +565,32 @@
       </c>
       <c r="H3" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
